--- a/doc/HealDB_Metadata.xlsx
+++ b/doc/HealDB_Metadata.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11595" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11595"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="5" r:id="rId1"/>
     <sheet name="Tables_Naming" sheetId="1" r:id="rId2"/>
-    <sheet name="Attribute_Naming" sheetId="2" r:id="rId3"/>
+    <sheet name="Attributes_Naming" sheetId="2" r:id="rId3"/>
     <sheet name="Tables_Overview" sheetId="3" r:id="rId4"/>
     <sheet name="Data_Dictionary" sheetId="4" r:id="rId5"/>
   </sheets>
@@ -66,9 +66,6 @@
     <t>1. Tables_Naming</t>
   </si>
   <si>
-    <t>2. Fields_Naming</t>
-  </si>
-  <si>
     <t>4. Data_Dictionary</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
   </si>
   <si>
     <t>Define prefixes and table categories</t>
-  </si>
-  <si>
-    <t>Field naming standard</t>
   </si>
   <si>
     <t>Ensure consistency in column names</t>
@@ -2133,6 +2127,12 @@
       </rPr>
       <t xml:space="preserve"> to ensure translation accuracy. In the working table, this field is not yet populated but retains the same meaning.</t>
     </r>
+  </si>
+  <si>
+    <t>2. Attributes_Naming</t>
+  </si>
+  <si>
+    <t>Attribute naming standard</t>
   </si>
 </sst>
 </file>
@@ -2805,13 +2805,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2819,43 +2819,43 @@
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>12</v>
+        <v>491</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>20</v>
+        <v>492</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2895,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -2907,19 +2907,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -2971,164 +2971,164 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3151,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>9</v>
@@ -3162,442 +3162,442 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B28" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B29" t="s">
+        <v>480</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B30" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B32" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B33" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B34" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>478</v>
+      </c>
+      <c r="B35" t="s">
         <v>480</v>
       </c>
-      <c r="B35" t="s">
-        <v>482</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B36" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -3626,25 +3626,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>8</v>
@@ -3652,4968 +3652,4968 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" t="s">
         <v>123</v>
       </c>
-      <c r="C3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" t="s">
-        <v>125</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" t="s">
         <v>90</v>
       </c>
-      <c r="F7" t="s">
-        <v>92</v>
-      </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" t="s">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
-        <v>92</v>
-      </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" t="s">
         <v>90</v>
       </c>
-      <c r="F12" t="s">
-        <v>92</v>
-      </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
         <v>90</v>
       </c>
-      <c r="F15" t="s">
-        <v>92</v>
-      </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" t="s">
         <v>90</v>
       </c>
-      <c r="F18" t="s">
-        <v>92</v>
-      </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s">
         <v>138</v>
       </c>
-      <c r="B19" t="s">
-        <v>140</v>
-      </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
         <v>90</v>
       </c>
-      <c r="F21" t="s">
-        <v>92</v>
-      </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="30">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G45" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E60" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G61" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="30">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D66" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F66" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G66" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D68" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="30">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="30">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G72" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G76" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B77" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E77" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D79" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E79" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F79" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G79" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G80" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C81" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G81" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E82" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F82" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G82" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C83" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C84" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G84" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="30">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E85" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C86" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G86" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="30">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C87" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E87" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G87" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D88" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D89" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E89" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F89" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G89" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D90" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E90" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F90" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G90" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="45">
       <c r="A91" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D91" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E91" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F91" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G91" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="30">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E92" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F92" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G92" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B93" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C94" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E94" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F94" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G94" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C95" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E95" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F95" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G95" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B96" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D96" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F96" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G96" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D97" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E97" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F97" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G97" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D98" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E98" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F98" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G98" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E99" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F99" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G99" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C100" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E100" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F100" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C101" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E101" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F101" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G101" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C102" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E102" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F102" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G102" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="30">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C103" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D103" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E103" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F103" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="30">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C104" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D104" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E104" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F104" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G104" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="30">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D105" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E105" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F105" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G105" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="30">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E106" t="s">
+        <v>88</v>
+      </c>
+      <c r="F106" t="s">
         <v>90</v>
       </c>
-      <c r="F106" t="s">
-        <v>92</v>
-      </c>
       <c r="G106" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D107" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E107" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F107" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G107" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C108" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E108" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F108" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G108" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D109" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E109" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F109" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G109" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E110" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F110" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G110" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C111" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D111" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E111" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F111" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G111" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D112" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E112" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F112" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G112" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C113" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D113" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E113" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F113" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G113" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="30">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G114" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D115" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E115" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F115" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G115" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B116" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C116" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D116" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E116" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F116" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G116" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D117" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E117" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F117" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G117" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="30">
       <c r="A118" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C118" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D118" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F118" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G118" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B119" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D119" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E119" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F119" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G119" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B120" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C120" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D120" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E120" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F120" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G120" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B121" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C121" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E121" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F121" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B122" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C122" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D122" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E122" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F122" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G122" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B123" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C123" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D123" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E123" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F123" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G123" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B124" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C124" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D124" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E124" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F124" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G124" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B125" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C125" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D125" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E125" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F125" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G125" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B126" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C126" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D126" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E126" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F126" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G126" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D127" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E127" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F127" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G127" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C128" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D128" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E128" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F128" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G128" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B129" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C129" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D129" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E129" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F129" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G129" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D130" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E130" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F130" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G130" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C131" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D131" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E131" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F131" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G131" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B132" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D132" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E132" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F132" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G132" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B133" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C133" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D133" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E133" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F133" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G133" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B134" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C134" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E134" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F134" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G134" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B135" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C135" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D135" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E135" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F135" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G135" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B136" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C136" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G136" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B137" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D137" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E137" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F137" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G137" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B138" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C138" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D138" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E138" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F138" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G138" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B139" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C139" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D139" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E139" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F139" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G139" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D140" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E140" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F140" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G140" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D141" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E141" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F141" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G141" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B142" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C142" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D142" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E142" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F142" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G142" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B143" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C143" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D143" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E143" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F143" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G143" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B144" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D144" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E144" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F144" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="30">
       <c r="A145" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B145" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C145" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D145" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E145" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F145" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G145" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C146" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D146" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E146" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F146" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G146" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B147" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C147" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D147" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E147" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F147" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G147" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="30">
       <c r="A148" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B148" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C148" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D148" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E148" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F148" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G148" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B149" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C149" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E149" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F149" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G149" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C150" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D150" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E150" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F150" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G150" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B151" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C151" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D151" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E151" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F151" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G151" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B152" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C152" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D152" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E152" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F152" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G152" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B153" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C153" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D153" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E153" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F153" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G153" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B154" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C154" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D154" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E154" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F154" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G154" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B155" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C155" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D155" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E155" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F155" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G155" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B156" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C156" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D156" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E156" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F156" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G156" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B157" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C157" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D157" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E157" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F157" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G157" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B158" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C158" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D158" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E158" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F158" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G158" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B159" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C159" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D159" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E159" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F159" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G159" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B160" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C160" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D160" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E160" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F160" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G160" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B161" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C161" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D161" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E161" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F161" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G161" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B162" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C162" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D162" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E162" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F162" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G162" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B163" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C163" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D163" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E163" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F163" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G163" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="45">
       <c r="A164" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B164" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C164" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D164" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E164" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F164" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G164" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B165" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C165" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D165" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E165" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F165" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G165" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="30">
       <c r="A166" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B166" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C166" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D166" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E166" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F166" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G166" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B167" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C167" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D167" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E167" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F167" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G167" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="45">
       <c r="A168" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B168" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C168" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D168" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E168" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F168" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G168" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B169" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C169" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D169" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E169" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F169" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G169" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="30">
       <c r="A170" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B170" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C170" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D170" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E170" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F170" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G170" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B171" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C171" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D171" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E171" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F171" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G171" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B172" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C172" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D172" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E172" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F172" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G172" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B173" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C173" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D173" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E173" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F173" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G173" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B174" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C174" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D174" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E174" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F174" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G174" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B175" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D175" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E175" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F175" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G175" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B176" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C176" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D176" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E176" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F176" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G176" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B177" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C177" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D177" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E177" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F177" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G177" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B178" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C178" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D178" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E178" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F178" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G178" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H178" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="30">
       <c r="A179" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B179" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C179" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D179" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F179" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G179" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="30">
       <c r="A180" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B180" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C180" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D180" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E180" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F180" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G180" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B181" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C181" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D181" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E181" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F181" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G181" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B182" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C182" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D182" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E182" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F182" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G182" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B183" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C183" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G183" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B184" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C184" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D184" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E184" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F184" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G184" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="30">
       <c r="A185" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B185" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C185" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D185" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E185" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F185" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G185" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="30">
       <c r="A186" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B186" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C186" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D186" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E186" t="s">
+        <v>88</v>
+      </c>
+      <c r="F186" t="s">
         <v>90</v>
       </c>
-      <c r="F186" t="s">
-        <v>92</v>
-      </c>
       <c r="G186" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="30">
       <c r="A187" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B187" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C187" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D187" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E187" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F187" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G187" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="30">
       <c r="A188" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B188" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C188" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D188" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E188" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F188" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G188" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B189" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C189" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D189" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E189" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F189" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G189" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="30">
       <c r="A190" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B190" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C190" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D190" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E190" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F190" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G190" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B191" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C191" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D191" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E191" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F191" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G191" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="30">
       <c r="A192" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B192" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C192" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D192" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E192" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F192" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G192" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/doc/HealDB_Metadata.xlsx
+++ b/doc/HealDB_Metadata.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Attributes_Naming" sheetId="2" r:id="rId3"/>
     <sheet name="Tables_Overview" sheetId="3" r:id="rId4"/>
     <sheet name="Data_Dictionary" sheetId="4" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="528">
   <si>
     <t>db_</t>
   </si>
@@ -336,9 +337,6 @@
     <t>hd_int_med_disease_api_response</t>
   </si>
   <si>
-    <t>hd_int_med_disease_map</t>
-  </si>
-  <si>
     <t>hd_medication_active_ingredient</t>
   </si>
   <si>
@@ -1155,9 +1153,6 @@
     <t>The complete content of the drug leaflet file in binary format.</t>
   </si>
   <si>
-    <t>Extracted text from the "Indications" section of the drug leaflet, describing what the medication is used for.</t>
-  </si>
-  <si>
     <t>Extracted text from the section 'What should I know before using this medication?' in the drug leaflet, providing important precaution information before using the medication.</t>
   </si>
   <si>
@@ -1258,9 +1253,6 @@
   </si>
   <si>
     <t>Identifies the medication associated with the drug leaflet.</t>
-  </si>
-  <si>
-    <t>Extracted text from the "Precautions" section of the drug leaflet, providing important precaution information before using the medication.</t>
   </si>
   <si>
     <t>First-level hierarchical code for symptoms.</t>
@@ -1346,12 +1338,6 @@
   </si>
   <si>
     <t>Final translation of the active ingredient into English, combining automated and reviewed translations.</t>
-  </si>
-  <si>
-    <t>Extracted text from the Indications section of the drug leaflet in Portuguese, describing the medical conditions for which the medication is used.</t>
-  </si>
-  <si>
-    <t>Translated text of the Indications section in English, generated using an automated translation model.</t>
   </si>
   <si>
     <t>Primary key and foreign key referencing hd_medication. Unique identifier linking the translated leaflet section to a specific medication.</t>
@@ -2133,6 +2119,202 @@
   </si>
   <si>
     <t>Attribute naming standard</t>
+  </si>
+  <si>
+    <t>hd_int_med_disease_entity</t>
+  </si>
+  <si>
+    <t>Stores trait-level attributes extracted from ACM API responses for each disease or symptom entity linked to a medication.</t>
+  </si>
+  <si>
+    <t>hd_int_med_disease_trait</t>
+  </si>
+  <si>
+    <t>ds_functionality</t>
+  </si>
+  <si>
+    <t>Extracted text from the section 'How this medication works?' in the drug leaflet, providing important precaution information before using the medication.</t>
+  </si>
+  <si>
+    <t>ds_functionality_eng</t>
+  </si>
+  <si>
+    <t>Extracted text from the section 'What is this medication indicated for?' in the drug leaflet in Portuguese, describing what the medication is used for.</t>
+  </si>
+  <si>
+    <t>Extracted text from the section 'How this medication works?' in the drug leaflet in Portuguese, providing important precaution information before using the medication.</t>
+  </si>
+  <si>
+    <t>Translated text of the section 'How this medication works?' in English, generated using an automated translation model.</t>
+  </si>
+  <si>
+    <t>Translated text of the section 'What is this medication indicated for?' in English, generated using an automated translation model.</t>
+  </si>
+  <si>
+    <t>Part of the composite primary key (id_medication, cd_icd_full). Full ICD-10-CM code associated with the detected medical condition.</t>
+  </si>
+  <si>
+    <t>fl_low_confidence</t>
+  </si>
+  <si>
+    <t>nm_trait_main</t>
+  </si>
+  <si>
+    <t>vl_trait_main_score</t>
+  </si>
+  <si>
+    <t>tinyint</t>
+  </si>
+  <si>
+    <t>Relevance or confidence score of the medication-disease association.</t>
+  </si>
+  <si>
+    <t>Score indicating the relevance of the extracted entity within the text.</t>
+  </si>
+  <si>
+    <t>Flag indicating whether the association has low confidence (1 = yes, 0 = no).</t>
+  </si>
+  <si>
+    <t>Name of the main trait or characteristic identified in the entity association.</t>
+  </si>
+  <si>
+    <t>Score related to the strength or relevance of the main trait identified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nm_trait  </t>
+  </si>
+  <si>
+    <t>vl_trait_score</t>
+  </si>
+  <si>
+    <t>Confidence score or weight assigned to the specific trait within the context of the disease-medication relation.</t>
+  </si>
+  <si>
+    <t>Name of the trait (qualifier, modifier, or property) associated with the disease entity in the ACM API output.</t>
+  </si>
+  <si>
+    <t>Campo</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Not Null</t>
+  </si>
+  <si>
+    <t>Descrição (EN)</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <r>
+      <t>✅ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hd_medication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Part of the composite primary key (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>id_medication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cd_icd_full</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). Foreign key referencing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hd_medication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Identifies the medication associated with the inferred ICD-10-CM codes.</t>
+    </r>
+  </si>
+  <si>
+    <t>varchar(150)</t>
+  </si>
+  <si>
+    <t>nm_trait</t>
+  </si>
+  <si>
+    <t>❌</t>
+  </si>
+  <si>
+    <t>ds_cat_eng</t>
+  </si>
+  <si>
+    <t>ds_group_eng</t>
+  </si>
+  <si>
+    <t>ds_subcat_eng</t>
+  </si>
+  <si>
+    <t>Description of the subcategory in English.</t>
+  </si>
+  <si>
+    <t>Description of the disease group in English.</t>
+  </si>
+  <si>
+    <t>Description of the disease category in English.</t>
   </si>
 </sst>
 </file>
@@ -2174,15 +2356,21 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2190,11 +2378,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="thin">
+        <color theme="6"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2224,6 +2427,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2504,7 +2713,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="A1:C41" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="A1:C42" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:C42"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Table Name" dataDxfId="4"/>
     <tableColumn id="2" name="Table Type" dataDxfId="3"/>
@@ -2515,8 +2725,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabela5" displayName="Tabela5" ref="A1:H192" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:H192"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabela5" displayName="Tabela5" ref="A1:H208" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H208"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Table Name"/>
     <tableColumn id="2" name="Column Name"/>
@@ -2827,10 +3037,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>19</v>
@@ -2895,7 +3105,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -2907,19 +3117,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -2931,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -2943,7 +3153,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -3141,7 +3351,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -3165,10 +3375,10 @@
         <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3176,10 +3386,10 @@
         <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3187,10 +3397,10 @@
         <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3198,21 +3408,21 @@
         <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3220,10 +3430,10 @@
         <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3231,10 +3441,10 @@
         <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3242,10 +3452,10 @@
         <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3253,10 +3463,10 @@
         <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3264,10 +3474,10 @@
         <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3275,10 +3485,10 @@
         <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3286,10 +3496,10 @@
         <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3297,10 +3507,10 @@
         <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3308,10 +3518,10 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3322,282 +3532,293 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>261</v>
+      <c r="A18" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
         <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
         <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
         <v>72</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>471</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
-        <v>480</v>
+        <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>481</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B29" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B30" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B31" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>469</v>
+      </c>
+      <c r="B32" t="s">
         <v>475</v>
       </c>
-      <c r="B32" t="s">
-        <v>480</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B33" t="s">
+        <v>475</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B34" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B35" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B36" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>474</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>475</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>271</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>89</v>
       </c>
-      <c r="B41" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>275</v>
+      <c r="B42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3610,7 +3831,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:J257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -3621,7 +3842,9 @@
     <col min="6" max="6" width="21.7109375" style="9" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" style="9" customWidth="1"/>
     <col min="8" max="8" width="108.5703125" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="9"/>
+    <col min="9" max="9" width="9.140625" style="9"/>
+    <col min="10" max="10" width="32.85546875" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3655,10 +3878,10 @@
         <v>90</v>
       </c>
       <c r="B2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" t="s">
         <v>119</v>
-      </c>
-      <c r="C2" t="s">
-        <v>120</v>
       </c>
       <c r="D2" t="s">
         <v>85</v>
@@ -3673,7 +3896,7 @@
         <v>84</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3681,11 +3904,11 @@
         <v>90</v>
       </c>
       <c r="B3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" t="s">
         <v>121</v>
       </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
       <c r="D3" t="s">
         <v>83</v>
       </c>
@@ -3696,10 +3919,10 @@
         <v>83</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3707,11 +3930,11 @@
         <v>90</v>
       </c>
       <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
         <v>124</v>
       </c>
-      <c r="C4" t="s">
-        <v>125</v>
-      </c>
       <c r="D4" t="s">
         <v>83</v>
       </c>
@@ -3722,10 +3945,10 @@
         <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3733,10 +3956,10 @@
         <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
         <v>83</v>
@@ -3748,10 +3971,10 @@
         <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3759,11 +3982,11 @@
         <v>90</v>
       </c>
       <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
         <v>127</v>
       </c>
-      <c r="C6" t="s">
-        <v>128</v>
-      </c>
       <c r="D6" t="s">
         <v>83</v>
       </c>
@@ -3774,10 +3997,10 @@
         <v>83</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3785,10 +4008,10 @@
         <v>91</v>
       </c>
       <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
         <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>85</v>
@@ -3803,7 +4026,7 @@
         <v>84</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3811,10 +4034,10 @@
         <v>91</v>
       </c>
       <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
         <v>129</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
       </c>
       <c r="D8" t="s">
         <v>85</v>
@@ -3826,10 +4049,10 @@
         <v>83</v>
       </c>
       <c r="G8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3837,11 +4060,11 @@
         <v>91</v>
       </c>
       <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
         <v>131</v>
       </c>
-      <c r="C9" t="s">
-        <v>132</v>
-      </c>
       <c r="D9" t="s">
         <v>83</v>
       </c>
@@ -3852,10 +4075,10 @@
         <v>83</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3863,10 +4086,10 @@
         <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>85</v>
@@ -3881,7 +4104,7 @@
         <v>84</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3889,10 +4112,10 @@
         <v>92</v>
       </c>
       <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
         <v>119</v>
-      </c>
-      <c r="C11" t="s">
-        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>83</v>
@@ -3907,7 +4130,7 @@
         <v>84</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3915,10 +4138,10 @@
         <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
         <v>83</v>
@@ -3933,7 +4156,7 @@
         <v>84</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3941,10 +4164,10 @@
         <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
         <v>83</v>
@@ -3956,10 +4179,10 @@
         <v>83</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3967,10 +4190,10 @@
         <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>85</v>
@@ -3985,7 +4208,7 @@
         <v>84</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3993,10 +4216,10 @@
         <v>93</v>
       </c>
       <c r="B15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
         <v>119</v>
-      </c>
-      <c r="C15" t="s">
-        <v>120</v>
       </c>
       <c r="D15" t="s">
         <v>83</v>
@@ -4011,7 +4234,7 @@
         <v>84</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4019,10 +4242,10 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
         <v>83</v>
@@ -4034,21 +4257,21 @@
         <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
         <v>136</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
         <v>85</v>
@@ -4063,18 +4286,18 @@
         <v>84</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
         <v>119</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>83</v>
@@ -4089,18 +4312,18 @@
         <v>84</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
         <v>83</v>
@@ -4112,21 +4335,21 @@
         <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>85</v>
@@ -4141,18 +4364,18 @@
         <v>84</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
         <v>119</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>83</v>
@@ -4167,18 +4390,18 @@
         <v>84</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>83</v>
@@ -4190,10 +4413,10 @@
         <v>83</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4204,7 +4427,7 @@
         <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
         <v>85</v>
@@ -4219,7 +4442,7 @@
         <v>84</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4227,10 +4450,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
         <v>83</v>
@@ -4245,7 +4468,7 @@
         <v>84</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30">
@@ -4256,7 +4479,7 @@
         <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>85</v>
@@ -4271,7 +4494,7 @@
         <v>84</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30">
@@ -4282,7 +4505,7 @@
         <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>85</v>
@@ -4294,10 +4517,10 @@
         <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4308,7 +4531,7 @@
         <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
         <v>85</v>
@@ -4320,10 +4543,10 @@
         <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4331,10 +4554,10 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>83</v>
@@ -4346,10 +4569,10 @@
         <v>83</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4357,11 +4580,11 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
         <v>143</v>
       </c>
-      <c r="C29" t="s">
-        <v>144</v>
-      </c>
       <c r="D29" t="s">
         <v>83</v>
       </c>
@@ -4372,10 +4595,10 @@
         <v>83</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4383,10 +4606,10 @@
         <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
         <v>85</v>
@@ -4401,7 +4624,7 @@
         <v>84</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4409,10 +4632,10 @@
         <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>83</v>
@@ -4427,7 +4650,7 @@
         <v>84</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4435,10 +4658,10 @@
         <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
         <v>83</v>
@@ -4450,10 +4673,10 @@
         <v>83</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -4461,10 +4684,10 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>85</v>
@@ -4479,7 +4702,7 @@
         <v>84</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4487,11 +4710,11 @@
         <v>95</v>
       </c>
       <c r="B34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" t="s">
         <v>149</v>
       </c>
-      <c r="C34" t="s">
-        <v>150</v>
-      </c>
       <c r="D34" t="s">
         <v>83</v>
       </c>
@@ -4505,7 +4728,7 @@
         <v>84</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4513,11 +4736,11 @@
         <v>95</v>
       </c>
       <c r="B35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s">
         <v>151</v>
       </c>
-      <c r="C35" t="s">
-        <v>152</v>
-      </c>
       <c r="D35" t="s">
         <v>83</v>
       </c>
@@ -4528,10 +4751,10 @@
         <v>83</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4539,10 +4762,10 @@
         <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
         <v>85</v>
@@ -4557,7 +4780,7 @@
         <v>84</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4565,10 +4788,10 @@
         <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
         <v>83</v>
@@ -4583,7 +4806,7 @@
         <v>84</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4591,10 +4814,10 @@
         <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
         <v>83</v>
@@ -4609,7 +4832,7 @@
         <v>84</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4617,10 +4840,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
         <v>83</v>
@@ -4632,10 +4855,10 @@
         <v>83</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4643,10 +4866,10 @@
         <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
         <v>83</v>
@@ -4661,7 +4884,7 @@
         <v>84</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4669,10 +4892,10 @@
         <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
         <v>83</v>
@@ -4684,10 +4907,10 @@
         <v>83</v>
       </c>
       <c r="G41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="30">
@@ -4695,25 +4918,25 @@
         <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
         <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G42" t="s">
         <v>84</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4721,10 +4944,10 @@
         <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
         <v>83</v>
@@ -4739,7 +4962,7 @@
         <v>84</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4750,7 +4973,7 @@
         <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
         <v>83</v>
@@ -4765,18 +4988,18 @@
         <v>84</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
         <v>83</v>
@@ -4791,7 +5014,7 @@
         <v>84</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4799,10 +5022,10 @@
         <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
         <v>85</v>
@@ -4817,7 +5040,7 @@
         <v>84</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4825,10 +5048,10 @@
         <v>98</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
         <v>83</v>
@@ -4843,7 +5066,7 @@
         <v>84</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4851,11 +5074,11 @@
         <v>98</v>
       </c>
       <c r="B48" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" t="s">
         <v>162</v>
       </c>
-      <c r="C48" t="s">
-        <v>163</v>
-      </c>
       <c r="D48" t="s">
         <v>83</v>
       </c>
@@ -4869,7 +5092,7 @@
         <v>84</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4877,11 +5100,11 @@
         <v>98</v>
       </c>
       <c r="B49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" t="s">
         <v>164</v>
       </c>
-      <c r="C49" t="s">
-        <v>165</v>
-      </c>
       <c r="D49" t="s">
         <v>83</v>
       </c>
@@ -4895,7 +5118,7 @@
         <v>84</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4903,11 +5126,11 @@
         <v>98</v>
       </c>
       <c r="B50" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" t="s">
         <v>166</v>
       </c>
-      <c r="C50" t="s">
-        <v>167</v>
-      </c>
       <c r="D50" t="s">
         <v>83</v>
       </c>
@@ -4921,7 +5144,7 @@
         <v>84</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30">
@@ -4929,10 +5152,10 @@
         <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
         <v>83</v>
@@ -4944,10 +5167,10 @@
         <v>83</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -4955,11 +5178,11 @@
         <v>98</v>
       </c>
       <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
         <v>169</v>
       </c>
-      <c r="C52" t="s">
-        <v>170</v>
-      </c>
       <c r="D52" t="s">
         <v>83</v>
       </c>
@@ -4970,10 +5193,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -4981,10 +5204,10 @@
         <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
         <v>83</v>
@@ -4996,24 +5219,24 @@
         <v>83</v>
       </c>
       <c r="G53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>522</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E54" t="s">
         <v>83</v>
@@ -5022,10 +5245,10 @@
         <v>83</v>
       </c>
       <c r="G54" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>329</v>
+        <v>527</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5033,13 +5256,13 @@
         <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
         <v>83</v>
@@ -5051,7 +5274,7 @@
         <v>84</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5059,10 +5282,10 @@
         <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="D56" t="s">
         <v>83</v>
@@ -5077,7 +5300,7 @@
         <v>84</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5085,10 +5308,10 @@
         <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="D57" t="s">
         <v>83</v>
@@ -5103,7 +5326,7 @@
         <v>84</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5111,10 +5334,10 @@
         <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D58" t="s">
         <v>83</v>
@@ -5129,21 +5352,21 @@
         <v>84</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
         <v>83</v>
@@ -5155,33 +5378,27 @@
         <v>84</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>523</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
-      </c>
-      <c r="D60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" t="s">
-        <v>88</v>
-      </c>
-      <c r="F60" t="s">
-        <v>98</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
       <c r="G60" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>347</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5189,13 +5406,13 @@
         <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E61" t="s">
         <v>83</v>
@@ -5207,7 +5424,7 @@
         <v>84</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5215,25 +5432,25 @@
         <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C62" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F62" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G62" t="s">
         <v>84</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5241,10 +5458,10 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
         <v>83</v>
@@ -5259,18 +5476,18 @@
         <v>84</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="30">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="D64" t="s">
         <v>83</v>
@@ -5282,10 +5499,10 @@
         <v>83</v>
       </c>
       <c r="G64" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5293,10 +5510,10 @@
         <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C65" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D65" t="s">
         <v>83</v>
@@ -5308,21 +5525,21 @@
         <v>83</v>
       </c>
       <c r="G65" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="30">
       <c r="A66" t="s">
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="D66" t="s">
         <v>83</v>
@@ -5334,10 +5551,10 @@
         <v>83</v>
       </c>
       <c r="G66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5345,10 +5562,10 @@
         <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D67" t="s">
         <v>83</v>
@@ -5360,125 +5577,125 @@
         <v>83</v>
       </c>
       <c r="G67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F68" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>444</v>
+        <v>122</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" t="s">
+        <v>83</v>
+      </c>
+      <c r="F69" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" t="s">
+        <v>122</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>100</v>
+      </c>
+      <c r="B70" t="s">
+        <v>524</v>
+      </c>
+      <c r="C70" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" t="s">
+        <v>83</v>
+      </c>
+      <c r="F70" t="s">
+        <v>83</v>
+      </c>
+      <c r="G70" t="s">
+        <v>122</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
         <v>101</v>
       </c>
-      <c r="B69" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" t="s">
-        <v>183</v>
-      </c>
-      <c r="D69" t="s">
-        <v>83</v>
-      </c>
-      <c r="E69" t="s">
-        <v>83</v>
-      </c>
-      <c r="F69" t="s">
-        <v>83</v>
-      </c>
-      <c r="G69" t="s">
-        <v>123</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="30">
-      <c r="A70" t="s">
-        <v>102</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>75</v>
       </c>
-      <c r="C70" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" t="s">
-        <v>85</v>
-      </c>
-      <c r="E70" t="s">
-        <v>88</v>
-      </c>
-      <c r="F70" t="s">
-        <v>68</v>
-      </c>
-      <c r="G70" t="s">
-        <v>84</v>
-      </c>
-      <c r="H70" s="12" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="30">
-      <c r="A71" t="s">
-        <v>102</v>
-      </c>
-      <c r="B71" t="s">
-        <v>184</v>
-      </c>
       <c r="C71" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D71" t="s">
         <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F71" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G71" t="s">
         <v>84</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C72" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D72" t="s">
         <v>83</v>
@@ -5490,50 +5707,50 @@
         <v>83</v>
       </c>
       <c r="G72" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="30">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>189</v>
+        <v>119</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F73" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G73" t="s">
-        <v>123</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="30">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
         <v>83</v>
@@ -5542,21 +5759,21 @@
         <v>83</v>
       </c>
       <c r="G74" t="s">
-        <v>123</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>351</v>
+        <v>84</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D75" t="s">
         <v>83</v>
@@ -5568,21 +5785,21 @@
         <v>83</v>
       </c>
       <c r="G75" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C76" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
@@ -5594,21 +5811,21 @@
         <v>83</v>
       </c>
       <c r="G76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D77" t="s">
         <v>83</v>
@@ -5620,21 +5837,21 @@
         <v>83</v>
       </c>
       <c r="G77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="D78" t="s">
         <v>83</v>
@@ -5646,21 +5863,21 @@
         <v>83</v>
       </c>
       <c r="G78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
         <v>83</v>
@@ -5672,21 +5889,21 @@
         <v>83</v>
       </c>
       <c r="G79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="D80" t="s">
         <v>83</v>
@@ -5698,21 +5915,21 @@
         <v>83</v>
       </c>
       <c r="G80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>488</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C81" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="D81" t="s">
         <v>83</v>
@@ -5724,24 +5941,24 @@
         <v>83</v>
       </c>
       <c r="G81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>68</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="C82" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E82" t="s">
         <v>83</v>
@@ -5750,21 +5967,21 @@
         <v>83</v>
       </c>
       <c r="G82" t="s">
-        <v>84</v>
-      </c>
-      <c r="H82" s="12" t="s">
-        <v>364</v>
+        <v>122</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>68</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C83" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="D83" t="s">
         <v>83</v>
@@ -5776,24 +5993,24 @@
         <v>83</v>
       </c>
       <c r="G83" t="s">
-        <v>84</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="30">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>490</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E84" t="s">
         <v>83</v>
@@ -5805,44 +6022,44 @@
         <v>84</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>360</v>
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="30">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>120</v>
+        <v>519</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F85" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="G85" t="s">
         <v>84</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>447</v>
+        <v>498</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>68</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>508</v>
       </c>
       <c r="C86" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>83</v>
@@ -5854,36 +6071,36 @@
         <v>83</v>
       </c>
       <c r="G86" t="s">
-        <v>123</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="30">
+        <v>84</v>
+      </c>
+      <c r="H86" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>68</v>
+        <v>490</v>
       </c>
       <c r="B87" t="s">
-        <v>202</v>
+        <v>509</v>
       </c>
       <c r="C87" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="D87" t="s">
         <v>83</v>
       </c>
       <c r="E87" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F87" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="G87" t="s">
-        <v>123</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>448</v>
+        <v>122</v>
+      </c>
+      <c r="H87" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -5891,25 +6108,25 @@
         <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="C88" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E88" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F88" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G88" t="s">
         <v>84</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>449</v>
+        <v>363</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -5917,10 +6134,10 @@
         <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C89" t="s">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="D89" t="s">
         <v>83</v>
@@ -5935,7 +6152,7 @@
         <v>84</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -5943,10 +6160,10 @@
         <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>83</v>
@@ -5958,99 +6175,99 @@
         <v>83</v>
       </c>
       <c r="G90" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="45">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="30">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="C91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D91" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E91" t="s">
         <v>88</v>
       </c>
       <c r="F91" t="s">
+        <v>110</v>
+      </c>
+      <c r="G91" t="s">
+        <v>84</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
         <v>68</v>
       </c>
-      <c r="G91" t="s">
-        <v>84</v>
-      </c>
-      <c r="H91" s="11" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="30">
-      <c r="A92" t="s">
-        <v>103</v>
-      </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E92" t="s">
+        <v>83</v>
+      </c>
+      <c r="F92" t="s">
+        <v>83</v>
+      </c>
+      <c r="G92" t="s">
+        <v>122</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="30">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" t="s">
+        <v>119</v>
+      </c>
+      <c r="D93" t="s">
+        <v>83</v>
+      </c>
+      <c r="E93" t="s">
         <v>88</v>
       </c>
-      <c r="F92" t="s">
-        <v>69</v>
-      </c>
-      <c r="G92" t="s">
-        <v>84</v>
-      </c>
-      <c r="H92" s="11" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" t="s">
-        <v>104</v>
-      </c>
-      <c r="B93" t="s">
-        <v>214</v>
-      </c>
-      <c r="C93" t="s">
-        <v>120</v>
-      </c>
-      <c r="D93" t="s">
-        <v>85</v>
-      </c>
-      <c r="E93" t="s">
-        <v>83</v>
-      </c>
       <c r="F93" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="G93" t="s">
-        <v>84</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>365</v>
+        <v>122</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="C94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D94" t="s">
         <v>83</v>
@@ -6059,24 +6276,24 @@
         <v>88</v>
       </c>
       <c r="F94" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="G94" t="s">
         <v>84</v>
       </c>
-      <c r="H94" s="5" t="s">
-        <v>366</v>
+      <c r="H94" s="12" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D95" t="s">
         <v>83</v>
@@ -6090,149 +6307,149 @@
       <c r="G95" t="s">
         <v>84</v>
       </c>
-      <c r="H95" s="5" t="s">
-        <v>367</v>
+      <c r="H95" s="12" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="D96" t="s">
         <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F96" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G96" t="s">
-        <v>123</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="45">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E97" t="s">
         <v>88</v>
       </c>
       <c r="F97" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="G97" t="s">
-        <v>123</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H97" s="11" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="30">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B98" t="s">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E98" t="s">
         <v>88</v>
       </c>
       <c r="F98" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G98" t="s">
-        <v>123</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>370</v>
+        <v>84</v>
+      </c>
+      <c r="H98" s="11" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
         <v>85</v>
       </c>
       <c r="E99" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F99" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G99" t="s">
         <v>84</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>206</v>
+        <v>75</v>
       </c>
       <c r="C100" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>83</v>
       </c>
       <c r="E100" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F100" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G100" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="D101" t="s">
         <v>83</v>
@@ -6244,281 +6461,251 @@
         <v>83</v>
       </c>
       <c r="G101" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C102" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="D102" t="s">
         <v>83</v>
       </c>
       <c r="E102" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F102" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="G102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="30">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C103" t="s">
-        <v>211</v>
+        <v>119</v>
       </c>
       <c r="D103" t="s">
         <v>83</v>
       </c>
       <c r="E103" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F103" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G103" t="s">
-        <v>123</v>
-      </c>
-      <c r="H103" s="12" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="30">
+        <v>122</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>119</v>
       </c>
       <c r="D104" t="s">
         <v>83</v>
       </c>
       <c r="E104" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F104" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G104" t="s">
-        <v>123</v>
-      </c>
-      <c r="H104" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="30">
+        <v>122</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="C105" t="s">
-        <v>120</v>
-      </c>
-      <c r="D105" t="s">
-        <v>85</v>
-      </c>
-      <c r="E105" t="s">
-        <v>88</v>
-      </c>
-      <c r="F105" t="s">
-        <v>69</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
       <c r="G105" t="s">
-        <v>84</v>
-      </c>
-      <c r="H105" s="12" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="30">
+        <v>122</v>
+      </c>
+      <c r="H105" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
-      </c>
-      <c r="D106" t="s">
-        <v>85</v>
-      </c>
-      <c r="E106" t="s">
-        <v>88</v>
-      </c>
-      <c r="F106" t="s">
-        <v>90</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
       <c r="G106" t="s">
-        <v>84</v>
-      </c>
-      <c r="H106" s="12" t="s">
-        <v>451</v>
+        <v>122</v>
+      </c>
+      <c r="H106" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>158</v>
+        <v>499</v>
       </c>
       <c r="C107" t="s">
-        <v>120</v>
-      </c>
-      <c r="D107" t="s">
-        <v>85</v>
-      </c>
-      <c r="E107" t="s">
-        <v>88</v>
-      </c>
-      <c r="F107" t="s">
-        <v>97</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
       <c r="G107" t="s">
-        <v>84</v>
-      </c>
-      <c r="H107" s="12" t="s">
-        <v>452</v>
+        <v>122</v>
+      </c>
+      <c r="H107" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>213</v>
+        <v>500</v>
       </c>
       <c r="C108" t="s">
-        <v>125</v>
-      </c>
-      <c r="D108" t="s">
-        <v>83</v>
-      </c>
-      <c r="E108" t="s">
-        <v>83</v>
-      </c>
-      <c r="F108" t="s">
-        <v>83</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="s">
-        <v>84</v>
-      </c>
-      <c r="H108" s="12" t="s">
-        <v>453</v>
+        <v>122</v>
+      </c>
+      <c r="H108" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>218</v>
+        <v>501</v>
       </c>
       <c r="C109" t="s">
-        <v>120</v>
-      </c>
-      <c r="D109" t="s">
-        <v>85</v>
-      </c>
-      <c r="E109" t="s">
-        <v>88</v>
-      </c>
-      <c r="F109" t="s">
-        <v>93</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
       <c r="G109" t="s">
-        <v>84</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>385</v>
+        <v>122</v>
+      </c>
+      <c r="H109" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B110" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D110" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E110" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F110" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G110" t="s">
         <v>84</v>
       </c>
-      <c r="H110" s="12" t="s">
-        <v>386</v>
+      <c r="H110" s="5" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="C111" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D111" t="s">
         <v>83</v>
       </c>
       <c r="E111" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F111" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G111" t="s">
-        <v>84</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>392</v>
+        <v>122</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C112" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D112" t="s">
         <v>83</v>
@@ -6530,47 +6717,47 @@
         <v>83</v>
       </c>
       <c r="G112" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
       <c r="C113" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="D113" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E113" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F113" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G113" t="s">
-        <v>84</v>
-      </c>
-      <c r="H113" s="12" t="s">
-        <v>454</v>
+        <v>122</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="30">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B114" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C114" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="D114" t="s">
         <v>83</v>
@@ -6582,21 +6769,21 @@
         <v>83</v>
       </c>
       <c r="G114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="30">
       <c r="A115" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C115" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="D115" t="s">
         <v>83</v>
@@ -6608,21 +6795,21 @@
         <v>83</v>
       </c>
       <c r="G115" t="s">
-        <v>123</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H115" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="30">
       <c r="A116" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>491</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="D116" t="s">
         <v>83</v>
@@ -6634,21 +6821,21 @@
         <v>83</v>
       </c>
       <c r="G116" t="s">
-        <v>123</v>
-      </c>
-      <c r="H116" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="30">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B117" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="C117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D117" t="s">
         <v>85</v>
@@ -6657,76 +6844,76 @@
         <v>88</v>
       </c>
       <c r="F117" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="G117" t="s">
         <v>84</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="30">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B118" t="s">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E118" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F118" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B119" t="s">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D119" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E119" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F119" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G119" t="s">
-        <v>123</v>
-      </c>
-      <c r="H119" s="5" t="s">
-        <v>390</v>
+        <v>84</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B120" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C120" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D120" t="s">
         <v>83</v>
@@ -6738,47 +6925,47 @@
         <v>83</v>
       </c>
       <c r="G120" t="s">
-        <v>123</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>391</v>
+        <v>84</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B121" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D121" t="s">
         <v>85</v>
       </c>
       <c r="E121" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F121" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G121" t="s">
         <v>84</v>
       </c>
-      <c r="H121" s="5" t="s">
-        <v>382</v>
+      <c r="H121" s="12" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B122" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="C122" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D122" t="s">
         <v>83</v>
@@ -6792,45 +6979,45 @@
       <c r="G122" t="s">
         <v>84</v>
       </c>
-      <c r="H122" s="5" t="s">
-        <v>383</v>
+      <c r="H122" s="12" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C123" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="D123" t="s">
         <v>83</v>
       </c>
       <c r="E123" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F123" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G123" t="s">
         <v>84</v>
       </c>
-      <c r="H123" s="5" t="s">
-        <v>393</v>
+      <c r="H123" s="12" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="B124" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C124" t="s">
-        <v>201</v>
+        <v>124</v>
       </c>
       <c r="D124" t="s">
         <v>83</v>
@@ -6845,44 +7032,44 @@
         <v>84</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="B125" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C125" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D125" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E125" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F125" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G125" t="s">
         <v>84</v>
       </c>
-      <c r="H125" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+      <c r="H125" s="12" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="30">
       <c r="A126" t="s">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="B126" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C126" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D126" t="s">
         <v>83</v>
@@ -6894,21 +7081,21 @@
         <v>83</v>
       </c>
       <c r="G126" t="s">
-        <v>84</v>
-      </c>
-      <c r="H126" s="5" t="s">
-        <v>395</v>
+        <v>122</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="C127" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="D127" t="s">
         <v>83</v>
@@ -6920,21 +7107,21 @@
         <v>83</v>
       </c>
       <c r="G127" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="C128" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D128" t="s">
         <v>83</v>
@@ -6946,47 +7133,47 @@
         <v>83</v>
       </c>
       <c r="G128" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>472</v>
+        <v>109</v>
       </c>
       <c r="B129" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C129" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="D129" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E129" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F129" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G129" t="s">
         <v>84</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="30">
       <c r="A130" t="s">
-        <v>472</v>
+        <v>109</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C130" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="D130" t="s">
         <v>83</v>
@@ -6998,21 +7185,21 @@
         <v>83</v>
       </c>
       <c r="G130" t="s">
-        <v>84</v>
-      </c>
-      <c r="H130" s="5" t="s">
-        <v>394</v>
+        <v>122</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>472</v>
+        <v>109</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="C131" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="D131" t="s">
         <v>83</v>
@@ -7024,21 +7211,21 @@
         <v>83</v>
       </c>
       <c r="G131" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>472</v>
+        <v>109</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="C132" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D132" t="s">
         <v>83</v>
@@ -7050,24 +7237,24 @@
         <v>83</v>
       </c>
       <c r="G132" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>472</v>
+        <v>110</v>
       </c>
       <c r="B133" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C133" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="D133" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E133" t="s">
         <v>83</v>
@@ -7076,21 +7263,21 @@
         <v>83</v>
       </c>
       <c r="G133" t="s">
-        <v>123</v>
-      </c>
-      <c r="H133" s="12" t="s">
-        <v>399</v>
+        <v>84</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>472</v>
+        <v>110</v>
       </c>
       <c r="B134" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="C134" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="D134" t="s">
         <v>83</v>
@@ -7102,24 +7289,24 @@
         <v>83</v>
       </c>
       <c r="G134" t="s">
-        <v>123</v>
-      </c>
-      <c r="H134" s="12" t="s">
-        <v>400</v>
+        <v>84</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="B135" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="C135" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D135" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E135" t="s">
         <v>83</v>
@@ -7130,19 +7317,19 @@
       <c r="G135" t="s">
         <v>84</v>
       </c>
-      <c r="H135" s="12" t="s">
-        <v>401</v>
+      <c r="H135" s="5" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="B136" t="s">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="C136" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="D136" t="s">
         <v>83</v>
@@ -7156,19 +7343,19 @@
       <c r="G136" t="s">
         <v>84</v>
       </c>
-      <c r="H136" s="12" t="s">
-        <v>403</v>
+      <c r="H136" s="5" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="B137" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C137" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
         <v>83</v>
@@ -7180,21 +7367,21 @@
         <v>83</v>
       </c>
       <c r="G137" t="s">
-        <v>84</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>394</v>
+        <v>122</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="B138" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="C138" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D138" t="s">
         <v>83</v>
@@ -7206,24 +7393,24 @@
         <v>83</v>
       </c>
       <c r="G138" t="s">
-        <v>123</v>
-      </c>
-      <c r="H138" s="12" t="s">
-        <v>402</v>
+        <v>122</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>473</v>
+        <v>112</v>
       </c>
       <c r="B139" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C139" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D139" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E139" t="s">
         <v>83</v>
@@ -7232,26 +7419,26 @@
         <v>83</v>
       </c>
       <c r="G139" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="30">
       <c r="A140" t="s">
-        <v>473</v>
+        <v>112</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="C140" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D140" t="s">
         <v>83</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="11" t="s">
         <v>83</v>
       </c>
       <c r="F140" t="s">
@@ -7261,44 +7448,44 @@
         <v>84</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="30">
       <c r="A141" t="s">
-        <v>473</v>
+        <v>113</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="C141" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D141" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E141" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F141" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G141" t="s">
         <v>84</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>473</v>
+        <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>203</v>
+        <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="D142" t="s">
         <v>83</v>
@@ -7312,19 +7499,19 @@
       <c r="G142" t="s">
         <v>84</v>
       </c>
-      <c r="H142" s="12" t="s">
-        <v>406</v>
+      <c r="H142" s="5" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>473</v>
+        <v>113</v>
       </c>
       <c r="B143" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="C143" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="D143" t="s">
         <v>83</v>
@@ -7336,152 +7523,152 @@
         <v>83</v>
       </c>
       <c r="G143" t="s">
-        <v>123</v>
-      </c>
-      <c r="H143" s="12" t="s">
-        <v>407</v>
+        <v>122</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>474</v>
+        <v>113</v>
       </c>
       <c r="B144" t="s">
+        <v>238</v>
+      </c>
+      <c r="C144" t="s">
+        <v>121</v>
+      </c>
+      <c r="D144" t="s">
+        <v>83</v>
+      </c>
+      <c r="E144" t="s">
+        <v>83</v>
+      </c>
+      <c r="F144" t="s">
+        <v>83</v>
+      </c>
+      <c r="G144" t="s">
+        <v>122</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" t="s">
+        <v>113</v>
+      </c>
+      <c r="B145" t="s">
+        <v>240</v>
+      </c>
+      <c r="C145" t="s">
+        <v>121</v>
+      </c>
+      <c r="D145" t="s">
+        <v>83</v>
+      </c>
+      <c r="E145" t="s">
+        <v>83</v>
+      </c>
+      <c r="F145" t="s">
+        <v>83</v>
+      </c>
+      <c r="G145" t="s">
+        <v>122</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="30">
+      <c r="A146" t="s">
+        <v>113</v>
+      </c>
+      <c r="B146" t="s">
+        <v>239</v>
+      </c>
+      <c r="C146" t="s">
+        <v>162</v>
+      </c>
+      <c r="D146" t="s">
+        <v>83</v>
+      </c>
+      <c r="E146" t="s">
+        <v>83</v>
+      </c>
+      <c r="F146" t="s">
+        <v>83</v>
+      </c>
+      <c r="G146" t="s">
+        <v>122</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="30">
+      <c r="A147" t="s">
+        <v>113</v>
+      </c>
+      <c r="B147" t="s">
+        <v>118</v>
+      </c>
+      <c r="C147" t="s">
+        <v>119</v>
+      </c>
+      <c r="D147" t="s">
+        <v>83</v>
+      </c>
+      <c r="E147" t="s">
+        <v>88</v>
+      </c>
+      <c r="F147" t="s">
+        <v>90</v>
+      </c>
+      <c r="G147" t="s">
+        <v>122</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="30">
+      <c r="A148" t="s">
+        <v>114</v>
+      </c>
+      <c r="B148" t="s">
         <v>75</v>
       </c>
-      <c r="C144" t="s">
-        <v>120</v>
-      </c>
-      <c r="D144" t="s">
-        <v>83</v>
-      </c>
-      <c r="E144" t="s">
-        <v>83</v>
-      </c>
-      <c r="F144" t="s">
-        <v>83</v>
-      </c>
-      <c r="G144" t="s">
-        <v>84</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="30">
-      <c r="A145" t="s">
-        <v>474</v>
-      </c>
-      <c r="B145" t="s">
-        <v>226</v>
-      </c>
-      <c r="C145" t="s">
-        <v>122</v>
-      </c>
-      <c r="D145" t="s">
-        <v>83</v>
-      </c>
-      <c r="E145" t="s">
-        <v>83</v>
-      </c>
-      <c r="F145" t="s">
-        <v>83</v>
-      </c>
-      <c r="G145" t="s">
-        <v>84</v>
-      </c>
-      <c r="H145" s="11" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
-      <c r="A146" t="s">
-        <v>475</v>
-      </c>
-      <c r="B146" t="s">
-        <v>75</v>
-      </c>
-      <c r="C146" t="s">
-        <v>120</v>
-      </c>
-      <c r="D146" t="s">
-        <v>83</v>
-      </c>
-      <c r="E146" t="s">
-        <v>83</v>
-      </c>
-      <c r="F146" t="s">
-        <v>83</v>
-      </c>
-      <c r="G146" t="s">
-        <v>84</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" t="s">
-        <v>475</v>
-      </c>
-      <c r="B147" t="s">
+      <c r="C148" t="s">
+        <v>119</v>
+      </c>
+      <c r="D148" t="s">
+        <v>85</v>
+      </c>
+      <c r="E148" t="s">
+        <v>88</v>
+      </c>
+      <c r="F148" t="s">
+        <v>104</v>
+      </c>
+      <c r="G148" t="s">
+        <v>84</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="30">
+      <c r="A149" t="s">
+        <v>114</v>
+      </c>
+      <c r="B149" t="s">
+        <v>209</v>
+      </c>
+      <c r="C149" t="s">
         <v>210</v>
       </c>
-      <c r="C147" t="s">
-        <v>211</v>
-      </c>
-      <c r="D147" t="s">
-        <v>83</v>
-      </c>
-      <c r="E147" t="s">
-        <v>83</v>
-      </c>
-      <c r="F147" t="s">
-        <v>83</v>
-      </c>
-      <c r="G147" t="s">
-        <v>84</v>
-      </c>
-      <c r="H147" s="12" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="30">
-      <c r="A148" t="s">
-        <v>475</v>
-      </c>
-      <c r="B148" t="s">
-        <v>212</v>
-      </c>
-      <c r="C148" t="s">
-        <v>211</v>
-      </c>
-      <c r="D148" t="s">
-        <v>83</v>
-      </c>
-      <c r="E148" t="s">
-        <v>83</v>
-      </c>
-      <c r="F148" t="s">
-        <v>83</v>
-      </c>
-      <c r="G148" t="s">
-        <v>123</v>
-      </c>
-      <c r="H148" s="12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" t="s">
-        <v>476</v>
-      </c>
-      <c r="B149" t="s">
-        <v>227</v>
-      </c>
-      <c r="C149" t="s">
-        <v>163</v>
-      </c>
       <c r="D149" t="s">
         <v>83</v>
       </c>
@@ -7492,21 +7679,22 @@
         <v>83</v>
       </c>
       <c r="G149" t="s">
-        <v>123</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H149" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="J149" s="14"/>
+    </row>
+    <row r="150" spans="1:10" ht="30">
       <c r="A150" t="s">
-        <v>476</v>
+        <v>114</v>
       </c>
       <c r="B150" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D150" t="s">
         <v>83</v>
@@ -7518,21 +7706,22 @@
         <v>83</v>
       </c>
       <c r="G150" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>497</v>
+      </c>
+      <c r="J150" s="13"/>
+    </row>
+    <row r="151" spans="1:10" ht="30">
       <c r="A151" t="s">
-        <v>476</v>
+        <v>114</v>
       </c>
       <c r="B151" t="s">
-        <v>229</v>
+        <v>491</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D151" t="s">
         <v>83</v>
@@ -7544,21 +7733,22 @@
         <v>83</v>
       </c>
       <c r="G151" t="s">
-        <v>123</v>
-      </c>
-      <c r="H151" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H151" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="J151" s="14"/>
+    </row>
+    <row r="152" spans="1:10" ht="30">
       <c r="A152" t="s">
-        <v>476</v>
+        <v>114</v>
       </c>
       <c r="B152" t="s">
-        <v>230</v>
+        <v>493</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D152" t="s">
         <v>83</v>
@@ -7570,24 +7760,24 @@
         <v>83</v>
       </c>
       <c r="G152" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="30">
       <c r="A153" t="s">
-        <v>476</v>
+        <v>89</v>
       </c>
       <c r="B153" t="s">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="D153" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E153" t="s">
         <v>83</v>
@@ -7596,21 +7786,21 @@
         <v>83</v>
       </c>
       <c r="G153" t="s">
-        <v>123</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" t="s">
-        <v>476</v>
+        <v>89</v>
       </c>
       <c r="B154" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D154" t="s">
         <v>83</v>
@@ -7622,21 +7812,21 @@
         <v>83</v>
       </c>
       <c r="G154" t="s">
-        <v>123</v>
-      </c>
-      <c r="H154" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="30">
       <c r="A155" t="s">
-        <v>476</v>
+        <v>89</v>
       </c>
       <c r="B155" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D155" t="s">
         <v>83</v>
@@ -7648,21 +7838,21 @@
         <v>83</v>
       </c>
       <c r="G155" t="s">
-        <v>123</v>
-      </c>
-      <c r="H155" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B156" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
         <v>83</v>
@@ -7674,21 +7864,21 @@
         <v>83</v>
       </c>
       <c r="G156" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B157" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D157" t="s">
         <v>83</v>
@@ -7700,21 +7890,21 @@
         <v>83</v>
       </c>
       <c r="G157" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B158" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D158" t="s">
         <v>83</v>
@@ -7726,21 +7916,21 @@
         <v>83</v>
       </c>
       <c r="G158" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B159" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="C159" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D159" t="s">
         <v>83</v>
@@ -7752,21 +7942,21 @@
         <v>83</v>
       </c>
       <c r="G159" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="C160" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="D160" t="s">
         <v>83</v>
@@ -7780,19 +7970,19 @@
       <c r="G160" t="s">
         <v>84</v>
       </c>
-      <c r="H160" s="12" t="s">
-        <v>426</v>
+      <c r="H160" s="5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B161" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C161" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D161" t="s">
         <v>83</v>
@@ -7806,19 +7996,19 @@
       <c r="G161" t="s">
         <v>84</v>
       </c>
-      <c r="H161" s="12" t="s">
-        <v>427</v>
+      <c r="H161" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B162" t="s">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="C162" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="D162" t="s">
         <v>83</v>
@@ -7830,21 +8020,21 @@
         <v>83</v>
       </c>
       <c r="G162" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B163" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C163" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="D163" t="s">
         <v>83</v>
@@ -7856,21 +8046,21 @@
         <v>83</v>
       </c>
       <c r="G163" t="s">
-        <v>123</v>
-      </c>
-      <c r="H163" s="12" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="45">
+        <v>84</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B164" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D164" t="s">
         <v>83</v>
@@ -7882,21 +8072,21 @@
         <v>83</v>
       </c>
       <c r="G164" t="s">
-        <v>123</v>
-      </c>
-      <c r="H164" s="12" t="s">
-        <v>490</v>
+        <v>84</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B165" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C165" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D165" t="s">
         <v>83</v>
@@ -7908,21 +8098,21 @@
         <v>83</v>
       </c>
       <c r="G165" t="s">
-        <v>123</v>
-      </c>
-      <c r="H165" s="12" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="30">
+        <v>84</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="C166" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D166" t="s">
         <v>83</v>
@@ -7934,21 +8124,21 @@
         <v>83</v>
       </c>
       <c r="G166" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="C167" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D167" t="s">
         <v>83</v>
@@ -7960,21 +8150,21 @@
         <v>83</v>
       </c>
       <c r="G167" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="45">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="B168" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="D168" t="s">
         <v>83</v>
@@ -7986,24 +8176,24 @@
         <v>83</v>
       </c>
       <c r="G168" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>490</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B169" t="s">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="C169" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D169" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E169" t="s">
         <v>83</v>
@@ -8014,22 +8204,22 @@
       <c r="G169" t="s">
         <v>84</v>
       </c>
-      <c r="H169" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="30">
+      <c r="H169" s="12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B170" t="s">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="C170" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E170" t="s">
         <v>83</v>
@@ -8040,22 +8230,22 @@
       <c r="G170" t="s">
         <v>84</v>
       </c>
-      <c r="H170" s="5" t="s">
-        <v>442</v>
+      <c r="H170" s="12" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B171" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="C171" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="D171" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E171" t="s">
         <v>83</v>
@@ -8064,21 +8254,21 @@
         <v>83</v>
       </c>
       <c r="G171" t="s">
-        <v>84</v>
-      </c>
-      <c r="H171" s="5" t="s">
-        <v>443</v>
+        <v>122</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B172" t="s">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="C172" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="D172" t="s">
         <v>83</v>
@@ -8090,21 +8280,21 @@
         <v>83</v>
       </c>
       <c r="G172" t="s">
-        <v>123</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>439</v>
+        <v>122</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B173" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C173" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D173" t="s">
         <v>83</v>
@@ -8118,22 +8308,22 @@
       <c r="G173" t="s">
         <v>84</v>
       </c>
-      <c r="H173" s="5" t="s">
-        <v>440</v>
+      <c r="H173" s="12" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>112</v>
+        <v>468</v>
       </c>
       <c r="B174" t="s">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="C174" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D174" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E174" t="s">
         <v>83</v>
@@ -8144,19 +8334,19 @@
       <c r="G174" t="s">
         <v>84</v>
       </c>
-      <c r="H174" s="5" t="s">
-        <v>423</v>
+      <c r="H174" s="12" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>112</v>
+        <v>468</v>
       </c>
       <c r="B175" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="D175" t="s">
         <v>83</v>
@@ -8170,19 +8360,19 @@
       <c r="G175" t="s">
         <v>84</v>
       </c>
-      <c r="H175" s="5" t="s">
-        <v>425</v>
+      <c r="H175" s="12" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>112</v>
+        <v>468</v>
       </c>
       <c r="B176" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C176" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D176" t="s">
         <v>83</v>
@@ -8194,21 +8384,21 @@
         <v>83</v>
       </c>
       <c r="G176" t="s">
-        <v>123</v>
-      </c>
-      <c r="H176" s="5" t="s">
-        <v>422</v>
+        <v>122</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>112</v>
+        <v>469</v>
       </c>
       <c r="B177" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="C177" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D177" t="s">
         <v>83</v>
@@ -8220,24 +8410,24 @@
         <v>83</v>
       </c>
       <c r="G177" t="s">
-        <v>123</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="30">
       <c r="A178" t="s">
-        <v>113</v>
+        <v>469</v>
       </c>
       <c r="B178" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C178" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D178" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E178" t="s">
         <v>83</v>
@@ -8248,24 +8438,24 @@
       <c r="G178" t="s">
         <v>84</v>
       </c>
-      <c r="H178" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="30">
+      <c r="H178" s="11" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>113</v>
+        <v>470</v>
       </c>
       <c r="B179" t="s">
-        <v>246</v>
+        <v>75</v>
       </c>
       <c r="C179" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D179" t="s">
         <v>83</v>
       </c>
-      <c r="E179" s="11" t="s">
+      <c r="E179" t="s">
         <v>83</v>
       </c>
       <c r="F179" t="s">
@@ -8275,44 +8465,44 @@
         <v>84</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="30">
       <c r="A180" t="s">
-        <v>114</v>
+        <v>470</v>
       </c>
       <c r="B180" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="C180" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="D180" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E180" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F180" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G180" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="30">
       <c r="A181" t="s">
-        <v>114</v>
+        <v>470</v>
       </c>
       <c r="B181" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="C181" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="D181" t="s">
         <v>83</v>
@@ -8324,21 +8514,21 @@
         <v>83</v>
       </c>
       <c r="G181" t="s">
-        <v>84</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="30">
       <c r="A182" t="s">
-        <v>114</v>
+        <v>470</v>
       </c>
       <c r="B182" t="s">
-        <v>238</v>
+        <v>491</v>
       </c>
       <c r="C182" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="D182" t="s">
         <v>83</v>
@@ -8350,21 +8540,21 @@
         <v>83</v>
       </c>
       <c r="G182" t="s">
-        <v>123</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>433</v>
+        <v>122</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="B183" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C183" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="D183" t="s">
         <v>83</v>
@@ -8376,21 +8566,21 @@
         <v>83</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="B184" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C184" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="D184" t="s">
         <v>83</v>
@@ -8402,21 +8592,21 @@
         <v>83</v>
       </c>
       <c r="G184" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="30">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="B185" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D185" t="s">
         <v>83</v>
@@ -8428,73 +8618,73 @@
         <v>83</v>
       </c>
       <c r="G185" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="30">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="B186" t="s">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="C186" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="D186" t="s">
         <v>83</v>
       </c>
       <c r="E186" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F186" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G186" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="30">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>115</v>
+        <v>471</v>
       </c>
       <c r="B187" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="C187" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="D187" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E187" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F187" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="G187" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" ht="30">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>115</v>
+        <v>471</v>
       </c>
       <c r="B188" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C188" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="D188" t="s">
         <v>83</v>
@@ -8506,21 +8696,21 @@
         <v>83</v>
       </c>
       <c r="G188" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>115</v>
+        <v>471</v>
       </c>
       <c r="B189" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C189" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="D189" t="s">
         <v>83</v>
@@ -8532,24 +8722,24 @@
         <v>83</v>
       </c>
       <c r="G189" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" ht="30">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>89</v>
+        <v>471</v>
       </c>
       <c r="B190" t="s">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="C190" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="D190" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E190" t="s">
         <v>83</v>
@@ -8558,21 +8748,21 @@
         <v>83</v>
       </c>
       <c r="G190" t="s">
-        <v>84</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>378</v>
+        <v>122</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>89</v>
+        <v>471</v>
       </c>
       <c r="B191" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C191" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D191" t="s">
         <v>83</v>
@@ -8584,21 +8774,21 @@
         <v>83</v>
       </c>
       <c r="G191" t="s">
-        <v>84</v>
-      </c>
-      <c r="H191" s="12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" ht="30">
+        <v>122</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>89</v>
+        <v>471</v>
       </c>
       <c r="B192" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C192" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D192" t="s">
         <v>83</v>
@@ -8610,10 +8800,452 @@
         <v>83</v>
       </c>
       <c r="G192" t="s">
-        <v>84</v>
-      </c>
-      <c r="H192" s="12" t="s">
-        <v>380</v>
+        <v>122</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" t="s">
+        <v>471</v>
+      </c>
+      <c r="B193" t="s">
+        <v>236</v>
+      </c>
+      <c r="C193" t="s">
+        <v>131</v>
+      </c>
+      <c r="D193" t="s">
+        <v>83</v>
+      </c>
+      <c r="E193" t="s">
+        <v>83</v>
+      </c>
+      <c r="F193" t="s">
+        <v>83</v>
+      </c>
+      <c r="G193" t="s">
+        <v>122</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" t="s">
+        <v>472</v>
+      </c>
+      <c r="B194" t="s">
+        <v>77</v>
+      </c>
+      <c r="C194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D194" t="s">
+        <v>83</v>
+      </c>
+      <c r="E194" t="s">
+        <v>83</v>
+      </c>
+      <c r="F194" t="s">
+        <v>83</v>
+      </c>
+      <c r="G194" t="s">
+        <v>84</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" t="s">
+        <v>472</v>
+      </c>
+      <c r="B195" t="s">
+        <v>140</v>
+      </c>
+      <c r="C195" t="s">
+        <v>121</v>
+      </c>
+      <c r="D195" t="s">
+        <v>83</v>
+      </c>
+      <c r="E195" t="s">
+        <v>83</v>
+      </c>
+      <c r="F195" t="s">
+        <v>83</v>
+      </c>
+      <c r="G195" t="s">
+        <v>84</v>
+      </c>
+      <c r="H195" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" t="s">
+        <v>472</v>
+      </c>
+      <c r="B196" t="s">
+        <v>237</v>
+      </c>
+      <c r="C196" t="s">
+        <v>121</v>
+      </c>
+      <c r="D196" t="s">
+        <v>83</v>
+      </c>
+      <c r="E196" t="s">
+        <v>83</v>
+      </c>
+      <c r="F196" t="s">
+        <v>83</v>
+      </c>
+      <c r="G196" t="s">
+        <v>122</v>
+      </c>
+      <c r="H196" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
+        <v>472</v>
+      </c>
+      <c r="B197" t="s">
+        <v>238</v>
+      </c>
+      <c r="C197" t="s">
+        <v>121</v>
+      </c>
+      <c r="D197" t="s">
+        <v>83</v>
+      </c>
+      <c r="E197" t="s">
+        <v>83</v>
+      </c>
+      <c r="F197" t="s">
+        <v>83</v>
+      </c>
+      <c r="G197" t="s">
+        <v>122</v>
+      </c>
+      <c r="H197" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="45">
+      <c r="A198" t="s">
+        <v>472</v>
+      </c>
+      <c r="B198" t="s">
+        <v>239</v>
+      </c>
+      <c r="C198" t="s">
+        <v>162</v>
+      </c>
+      <c r="D198" t="s">
+        <v>83</v>
+      </c>
+      <c r="E198" t="s">
+        <v>83</v>
+      </c>
+      <c r="F198" t="s">
+        <v>83</v>
+      </c>
+      <c r="G198" t="s">
+        <v>122</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" t="s">
+        <v>472</v>
+      </c>
+      <c r="B199" t="s">
+        <v>118</v>
+      </c>
+      <c r="C199" t="s">
+        <v>119</v>
+      </c>
+      <c r="D199" t="s">
+        <v>83</v>
+      </c>
+      <c r="E199" t="s">
+        <v>83</v>
+      </c>
+      <c r="F199" t="s">
+        <v>83</v>
+      </c>
+      <c r="G199" t="s">
+        <v>122</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="30">
+      <c r="A200" t="s">
+        <v>473</v>
+      </c>
+      <c r="B200" t="s">
+        <v>77</v>
+      </c>
+      <c r="C200" t="s">
+        <v>119</v>
+      </c>
+      <c r="D200" t="s">
+        <v>83</v>
+      </c>
+      <c r="E200" t="s">
+        <v>83</v>
+      </c>
+      <c r="F200" t="s">
+        <v>83</v>
+      </c>
+      <c r="G200" t="s">
+        <v>122</v>
+      </c>
+      <c r="H200" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
+        <v>473</v>
+      </c>
+      <c r="B201" t="s">
+        <v>240</v>
+      </c>
+      <c r="C201" t="s">
+        <v>121</v>
+      </c>
+      <c r="D201" t="s">
+        <v>83</v>
+      </c>
+      <c r="E201" t="s">
+        <v>83</v>
+      </c>
+      <c r="F201" t="s">
+        <v>83</v>
+      </c>
+      <c r="G201" t="s">
+        <v>122</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="45">
+      <c r="A202" t="s">
+        <v>473</v>
+      </c>
+      <c r="B202" t="s">
+        <v>239</v>
+      </c>
+      <c r="C202" t="s">
+        <v>162</v>
+      </c>
+      <c r="D202" t="s">
+        <v>83</v>
+      </c>
+      <c r="E202" t="s">
+        <v>83</v>
+      </c>
+      <c r="F202" t="s">
+        <v>83</v>
+      </c>
+      <c r="G202" t="s">
+        <v>122</v>
+      </c>
+      <c r="H202" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>474</v>
+      </c>
+      <c r="B203" t="s">
+        <v>241</v>
+      </c>
+      <c r="C203" t="s">
+        <v>131</v>
+      </c>
+      <c r="D203" t="s">
+        <v>85</v>
+      </c>
+      <c r="E203" t="s">
+        <v>83</v>
+      </c>
+      <c r="F203" t="s">
+        <v>83</v>
+      </c>
+      <c r="G203" t="s">
+        <v>84</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="30">
+      <c r="A204" t="s">
+        <v>474</v>
+      </c>
+      <c r="B204" t="s">
+        <v>78</v>
+      </c>
+      <c r="C204" t="s">
+        <v>129</v>
+      </c>
+      <c r="D204" t="s">
+        <v>85</v>
+      </c>
+      <c r="E204" t="s">
+        <v>83</v>
+      </c>
+      <c r="F204" t="s">
+        <v>83</v>
+      </c>
+      <c r="G204" t="s">
+        <v>84</v>
+      </c>
+      <c r="H204" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" t="s">
+        <v>474</v>
+      </c>
+      <c r="B205" t="s">
+        <v>79</v>
+      </c>
+      <c r="C205" t="s">
+        <v>131</v>
+      </c>
+      <c r="D205" t="s">
+        <v>85</v>
+      </c>
+      <c r="E205" t="s">
+        <v>83</v>
+      </c>
+      <c r="F205" t="s">
+        <v>83</v>
+      </c>
+      <c r="G205" t="s">
+        <v>84</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>474</v>
+      </c>
+      <c r="B206" t="s">
+        <v>80</v>
+      </c>
+      <c r="C206" t="s">
+        <v>151</v>
+      </c>
+      <c r="D206" t="s">
+        <v>83</v>
+      </c>
+      <c r="E206" t="s">
+        <v>83</v>
+      </c>
+      <c r="F206" t="s">
+        <v>83</v>
+      </c>
+      <c r="G206" t="s">
+        <v>122</v>
+      </c>
+      <c r="H206" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>474</v>
+      </c>
+      <c r="B207" t="s">
+        <v>142</v>
+      </c>
+      <c r="C207" t="s">
+        <v>143</v>
+      </c>
+      <c r="D207" t="s">
+        <v>83</v>
+      </c>
+      <c r="E207" t="s">
+        <v>83</v>
+      </c>
+      <c r="F207" t="s">
+        <v>83</v>
+      </c>
+      <c r="G207" t="s">
+        <v>84</v>
+      </c>
+      <c r="H207" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>474</v>
+      </c>
+      <c r="B208" t="s">
+        <v>142</v>
+      </c>
+      <c r="C208" t="s">
+        <v>143</v>
+      </c>
+      <c r="D208" t="s">
+        <v>83</v>
+      </c>
+      <c r="E208" t="s">
+        <v>83</v>
+      </c>
+      <c r="F208" t="s">
+        <v>83</v>
+      </c>
+      <c r="G208" t="s">
+        <v>84</v>
+      </c>
+      <c r="H208" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" t="s">
+        <v>488</v>
+      </c>
+      <c r="B257" t="s">
+        <v>195</v>
+      </c>
+      <c r="C257" t="s">
+        <v>182</v>
+      </c>
+      <c r="D257" t="s">
+        <v>83</v>
+      </c>
+      <c r="E257" t="s">
+        <v>83</v>
+      </c>
+      <c r="F257" t="s">
+        <v>83</v>
+      </c>
+      <c r="G257" t="s">
+        <v>122</v>
+      </c>
+      <c r="H257" s="5" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -8623,4 +9255,112 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A9:F13"/>
+  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="75">
+      <c r="A10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60">
+      <c r="A11" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45">
+      <c r="A12" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45">
+      <c r="A13" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>